--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -388,6 +388,24 @@
   </si>
   <si>
     <t>二次闪避</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>道术倍率</t>
   </si>
   <si>
     <t>吸血</t>
@@ -662,12 +680,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1454,7 +1472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O40"/>
+  <dimension ref="C1:O52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -2300,548 +2318,992 @@
       <c r="O23" s="2"/>
     </row>
     <row r="24" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+      <c r="C24" s="2">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2001</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C25" s="1">
+    <row r="25" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="2">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2002</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="2">
+        <v>22</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2003</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="2">
+        <v>23</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2004</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="2">
+        <v>24</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>2005</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="2">
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>2006</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="2">
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>4</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>2001</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="2">
+        <v>27</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>4</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>2002</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>28</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2003</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="2">
+        <v>29</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="2">
+        <v>4</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2004</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="2">
+        <v>30</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>2005</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="2">
+        <v>31</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2006</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="1">
         <v>101</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C26" s="1">
-        <v>102</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="1">
-        <v>2</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C27" s="1">
-        <v>103</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
-        <v>2</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O27" s="2" t="s">
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C28" s="1">
-        <v>104</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="O37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
-        <v>2</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="1">
-        <v>107</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="1">
-        <v>2</v>
-      </c>
-      <c r="F29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
-        <v>2</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C30" s="1">
-        <v>109</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="1">
-        <v>2</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C31" s="1">
-        <v>110</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="1">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="1">
-        <v>2</v>
-      </c>
-      <c r="J31" s="1">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C32" s="1">
-        <v>111</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="4:15">
-      <c r="D33" s="2"/>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="1">
-        <v>305</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3</v>
-      </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>2</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1">
-        <v>306</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="1">
-        <v>3</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>2</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C36" s="1">
-        <v>307</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>-2</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>2</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="O37" s="2"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="1">
+        <v>102</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C39" s="1">
+        <v>103</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C40" s="1">
+        <v>104</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C41" s="1">
+        <v>107</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C42" s="1">
+        <v>109</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C43" s="1">
+        <v>110</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C44" s="1">
+        <v>111</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="4:15">
+      <c r="D45" s="2"/>
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C46" s="1">
+        <v>305</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>2</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C47" s="1">
+        <v>306</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
+        <v>2</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C48" s="1">
+        <v>307</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="1">
         <v>401</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="1">
         <v>4</v>
       </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1">
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
         <v>-2</v>
       </c>
-      <c r="H38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:14">
-      <c r="C40" s="2">
+      <c r="H50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
+      <c r="C52" s="2">
         <v>500</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="D52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="2">
         <v>5</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>93</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
